--- a/outputs/51289.xlsx
+++ b/outputs/51289.xlsx
@@ -20,12 +20,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t xml:space="preserve">dog</t>
   </si>
   <si>
     <t xml:space="preserve">cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dog4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dog1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dog3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dog2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cat3</t>
   </si>
 </sst>
 </file>
@@ -184,36 +208,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -472,100 +500,92 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="4.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="4.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="3.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="str">
-        <f aca="false">A1&amp;COUNTIFS($A$1:$H$1,A1,$A$2:$H$2,"&gt;"&amp;A2)+1</f>
-        <v>dog4</v>
-      </c>
-      <c r="B4" s="7" t="str">
-        <f aca="false">B1&amp;COUNTIFS($A$1:$H$1,B1,$A$2:$H$2,"&gt;"&amp;B2)+1</f>
-        <v>cat2</v>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f aca="false">C1&amp;COUNTIFS($A$1:$H$1,C1,$A$2:$H$2,"&gt;"&amp;C2)+1</f>
-        <v>dog1</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f aca="false">D1&amp;COUNTIFS($A$1:$H$1,D1,$A$2:$H$2,"&gt;"&amp;D2)+1</f>
-        <v>cat4</v>
-      </c>
-      <c r="E4" s="7" t="str">
-        <f aca="false">E1&amp;COUNTIFS($A$1:$H$1,E1,$A$2:$H$2,"&gt;"&amp;E2)+1</f>
-        <v>dog3</v>
-      </c>
-      <c r="F4" s="7" t="str">
-        <f aca="false">F1&amp;COUNTIFS($A$1:$H$1,F1,$A$2:$H$2,"&gt;"&amp;F2)+1</f>
-        <v>cat1</v>
-      </c>
-      <c r="G4" s="7" t="str">
-        <f aca="false">G1&amp;COUNTIFS($A$1:$H$1,G1,$A$2:$H$2,"&gt;"&amp;G2)+1</f>
-        <v>dog2</v>
-      </c>
-      <c r="H4" s="7" t="str">
-        <f aca="false">H1&amp;COUNTIFS($A$1:$H$1,H1,$A$2:$H$2,"&gt;"&amp;H2)+1</f>
-        <v>cat3</v>
+      <c r="A4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/51289.xlsx
+++ b/outputs/51289.xlsx
@@ -1,89 +1,210 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="4">
   <si>
-    <t xml:space="preserve">dog</t>
+    <t>dog</t>
   </si>
   <si>
-    <t xml:space="preserve">cat</t>
+    <t>cat</t>
   </si>
   <si>
-    <t xml:space="preserve">dog4</t>
+    <t>cat2</t>
   </si>
   <si>
-    <t xml:space="preserve">cat2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dog1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cat4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dog3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cat1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dog2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cat3</t>
+    <t>dog1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="0"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -93,19 +214,205 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="16">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thick">
         <color rgb="FF00B0F0"/>
       </left>
@@ -116,7 +423,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top style="thick">
@@ -125,7 +432,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right style="thick">
         <color rgb="FF00B0F0"/>
@@ -136,7 +443,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thick">
         <color rgb="FF00B0F0"/>
       </left>
@@ -147,7 +454,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -156,7 +463,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right style="thick">
         <color rgb="FF00B0F0"/>
@@ -167,7 +474,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFFF0000"/>
       </left>
@@ -182,150 +489,331 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00B0F0"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -360,241 +848,332 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="7"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3.27"/>
+    <col min="1" max="1" width="3.90909090909091" customWidth="1"/>
+    <col min="2" max="2" width="4.27272727272727" customWidth="1"/>
+    <col min="3" max="3" width="4.90909090909091" customWidth="1"/>
+    <col min="4" max="4" width="3.27272727272727" customWidth="1"/>
+    <col min="5" max="5" width="3.90909090909091" customWidth="1"/>
+    <col min="6" max="6" width="4.27272727272727" customWidth="1"/>
+    <col min="7" max="7" width="4.90909090909091" customWidth="1"/>
+    <col min="8" max="8" width="3.27272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+    <row r="2" spans="1:8">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="5">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="5">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="5">
         <v>2</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="5">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="5">
         <v>8</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="5">
         <v>4</v>
       </c>
-      <c r="H2" s="7" t="n">
+      <c r="H2" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>9</v>
-      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>